--- a/docs/detail-design/10_Phong.xlsx
+++ b/docs/detail-design/10_Phong.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="160">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · PHÒNG &amp; BẢNG GIÁ</t>
   </si>
@@ -136,6 +136,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Thẻ phòng: nhãn giá "{N} giờ đầu" đổi theo số giờ tối thiểu (trước đây cố định "2 giờ đầu").</t>
+  </si>
+  <si>
     <t>Ảnh 1. Tab Phòng (Quản lý)</t>
   </si>
   <si>
@@ -262,7 +268,7 @@
     <t>tiền</t>
   </si>
   <si>
-    <t>Giá thật áp dụng (theo hạng hoặc giá riêng của phòng): "2 giờ đầu" + "+{giá}/giờ", "Qua đêm", "Theo ngày". Nhãn "2 giờ đầu" cố định, không đổi theo số giờ tối thiểu.</t>
+    <t>Giá thật áp dụng (theo hạng hoặc giá riêng của phòng): "{số giờ tối thiểu} giờ đầu" + "+{giá}/giờ", "Qua đêm", "Theo ngày". Nhãn giờ đầu đổi theo số giờ tối thiểu của bảng giá (minHours()).</t>
   </si>
   <si>
     <t>Đã dọn</t>
@@ -1124,7 +1130,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -1855,8 +1861,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -1896,6 +1944,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -1915,7 +1967,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -1951,7 +2003,7 @@
     </row>
     <row r="58" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B58" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
@@ -1987,7 +2039,7 @@
     </row>
     <row r="93" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -2023,7 +2075,7 @@
     </row>
     <row r="128" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B128" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
@@ -2083,7 +2135,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2119,10 +2171,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2133,22 +2185,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2156,12 +2208,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2174,33 +2226,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2208,12 +2260,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2226,33 +2278,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2260,12 +2312,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2278,33 +2330,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2312,12 +2364,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2330,33 +2382,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2364,12 +2416,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2382,33 +2434,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -2416,12 +2468,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -2434,33 +2486,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -2468,12 +2520,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -2481,38 +2533,38 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
     </row>
-    <row r="9" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="9" ht="95" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="6">
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -2520,12 +2572,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -2538,33 +2590,33 @@
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -2572,12 +2624,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -2590,33 +2642,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -2624,12 +2676,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -2642,33 +2694,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -2676,12 +2728,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -2691,7 +2743,7 @@
     </row>
     <row r="14" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -2727,10 +2779,10 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
@@ -2741,22 +2793,22 @@
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
@@ -2764,12 +2816,12 @@
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
       <c r="Y15" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z15" s="5"/>
       <c r="AA15" s="5"/>
       <c r="AB15" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
@@ -2782,33 +2834,33 @@
         <v>11</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -2816,12 +2868,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2834,33 +2886,33 @@
         <v>12</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -2868,12 +2920,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2886,33 +2938,33 @@
         <v>13</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -2920,12 +2972,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2938,33 +2990,33 @@
         <v>14</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -2972,12 +3024,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2987,7 +3039,7 @@
     </row>
     <row r="21" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -3023,10 +3075,10 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
@@ -3037,22 +3089,22 @@
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T22" s="5"/>
       <c r="U22" s="5"/>
@@ -3060,12 +3112,12 @@
       <c r="W22" s="5"/>
       <c r="X22" s="5"/>
       <c r="Y22" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z22" s="5"/>
       <c r="AA22" s="5"/>
       <c r="AB22" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
@@ -3078,33 +3130,33 @@
         <v>15</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3112,12 +3164,12 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -3130,33 +3182,33 @@
         <v>16</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -3164,12 +3216,12 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -3182,33 +3234,33 @@
         <v>17</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3216,12 +3268,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3231,7 +3283,7 @@
     </row>
     <row r="27" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
@@ -3267,10 +3319,10 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -3281,22 +3333,22 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P28" s="5"/>
       <c r="Q28" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -3304,12 +3356,12 @@
       <c r="W28" s="5"/>
       <c r="X28" s="5"/>
       <c r="Y28" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
       <c r="AB28" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AC28" s="5"/>
       <c r="AD28" s="5"/>
@@ -3322,33 +3374,33 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -3356,12 +3408,12 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3374,33 +3426,33 @@
         <v>19</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R30" s="3"/>
       <c r="S30" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="T30" s="3"/>
       <c r="U30" s="3"/>
@@ -3408,12 +3460,12 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
       <c r="AB30" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3630,7 +3682,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3666,7 +3718,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -3702,10 +3754,10 @@
     </row>
     <row r="3" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D3" s="8"/>
       <c r="E3" s="8"/>
@@ -3740,10 +3792,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -3778,7 +3830,7 @@
     </row>
     <row r="6" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3814,7 +3866,7 @@
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -3822,13 +3874,13 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
       <c r="L7" s="5" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -3838,7 +3890,7 @@
       <c r="R7" s="5"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="U7" s="5"/>
       <c r="V7" s="5"/>
@@ -3856,7 +3908,7 @@
     </row>
     <row r="8" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -3864,13 +3916,13 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -3880,7 +3932,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
@@ -3898,7 +3950,7 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -3906,13 +3958,13 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -3922,7 +3974,7 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
@@ -3940,7 +3992,7 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
@@ -3948,13 +4000,13 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -3964,7 +4016,7 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
@@ -3982,7 +4034,7 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -3990,13 +4042,13 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -4006,7 +4058,7 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
@@ -4024,7 +4076,7 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -4032,13 +4084,13 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -4048,7 +4100,7 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
@@ -4066,7 +4118,7 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -4074,13 +4126,13 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
@@ -4090,7 +4142,7 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="3"/>
@@ -4108,7 +4160,7 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
